--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_324_R33.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_324_R33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0789</v>
+        <v>4.5632</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1305</v>
+        <v>5.3796</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0516</v>
+        <v>-0.8164</v>
       </c>
       <c r="G2" t="n">
         <v>4.6097</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5055</v>
+        <v>0.9897</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7853</v>
+        <v>1.0343</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2798</v>
+        <v>-0.0446</v>
       </c>
       <c r="V2" t="n">
         <v>-2.428</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3622</v>
+        <v>2.6794</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5133</v>
+        <v>1.5119</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8489</v>
+        <v>1.1674</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.42</v>
+        <v>1.2011</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1294</v>
+        <v>1.0505</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7095</v>
+        <v>0.1506</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5989</v>
+        <v>2.2594</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7997</v>
+        <v>1.684</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3986</v>
+        <v>0.5754</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0189</v>
+        <v>-1.0583</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3298</v>
+        <v>-0.6335</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6891</v>
+        <v>-0.4248</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.5515</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0876</v>
+        <v>3.0154</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1016</v>
+        <v>0.6201</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3214</v>
+        <v>0.59</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7802</v>
+        <v>0.0301</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1444</v>
+        <v>0.3943</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1444</v>
+        <v>1.214</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2775</v>
+        <v>2.3258</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6731</v>
+        <v>0.8802</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6043</v>
+        <v>1.4456</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2011</v>
+        <v>-0.42</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0505</v>
+        <v>-1.1294</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1506</v>
+        <v>0.7095</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2594</v>
+        <v>0.5989</v>
       </c>
       <c r="K4" t="n">
-        <v>1.684</v>
+        <v>-0.7997</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5754</v>
+        <v>1.3986</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0583</v>
+        <v>-1.0189</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6335</v>
+        <v>-0.3298</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4248</v>
+        <v>-0.6891</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4639</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.5515</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0154</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2182</v>
+        <v>1.0653</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7512</v>
+        <v>0.6884</v>
       </c>
       <c r="U4" t="n">
-        <v>0.467</v>
+        <v>0.3769</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3943</v>
+        <v>2.1444</v>
       </c>
       <c r="W4" t="n">
-        <v>1.214</v>
+        <v>2.1444</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1991</v>
+        <v>0.9364</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2733</v>
+        <v>0.8762</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0742</v>
+        <v>0.0602</v>
       </c>
       <c r="G5" t="n">
         <v>-1.7056</v>
@@ -844,13 +844,13 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>1.049</v>
+        <v>0.7863</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5138</v>
+        <v>1.1167</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4648</v>
+        <v>-0.3304</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. DIBARTOLOMEO</t>
+          <t>J. CLARK III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0873</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3136</v>
+        <v>-0.0473</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4008</v>
+        <v>0.573</v>
       </c>
       <c r="G6" t="n">
-        <v>0.777</v>
+        <v>-0.4787</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7971</v>
+        <v>0.5688</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0201</v>
+        <v>-1.0475</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8205</v>
+        <v>1.1262</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8401999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9802999999999999</v>
+        <v>-0.0438</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0435</v>
+        <v>-1.6048</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0431</v>
+        <v>-0.6012</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0004</v>
+        <v>-1.0037</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6959</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R6" t="n">
         <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5843</v>
+        <v>-0.1632</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6528</v>
+        <v>0.1614</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.3246</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1444</v>
+        <v>2.7912</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1444</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CLARK III</t>
+          <t>T. BLATT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5763</v>
+        <v>0.4737</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9476</v>
+        <v>-0.7006</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3713</v>
+        <v>1.1743</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4787</v>
+        <v>1.4435</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5688</v>
+        <v>1.437</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0475</v>
+        <v>0.0065</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1262</v>
+        <v>2.1334</v>
       </c>
       <c r="K7" t="n">
-        <v>1.17</v>
+        <v>1.2303</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0438</v>
+        <v>0.9032</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6048</v>
+        <v>-0.6899</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6012</v>
+        <v>0.2067</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0037</v>
+        <v>-0.8966</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.6237</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4793</v>
+        <v>-3.7112</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2652</v>
+        <v>0.0481</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7389</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5263</v>
+        <v>-0.6873</v>
       </c>
       <c r="V7" t="n">
-        <v>2.7912</v>
+        <v>0.1418</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1444</v>
+        <v>0.1418</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6468</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. BLATT</t>
+          <t>J. DIBARTOLOMEO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7874</v>
+        <v>-0.1977</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7936</v>
+        <v>1.2703</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0062</v>
+        <v>-1.468</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4435</v>
+        <v>0.777</v>
       </c>
       <c r="H8" t="n">
-        <v>1.437</v>
+        <v>0.7971</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0065</v>
+        <v>-0.0201</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1334</v>
+        <v>1.8205</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2303</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9032</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6899</v>
+        <v>-1.0435</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2067</v>
+        <v>-0.0431</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8966</v>
+        <v>-1.0004</v>
       </c>
       <c r="P8" t="n">
+        <v>0.6959</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-3.7112</v>
-      </c>
       <c r="R8" t="n">
-        <v>2.5515</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2129</v>
+        <v>0.4738</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3576</v>
+        <v>0.6095</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.1357</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1418</v>
+        <v>-2.1444</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1174</v>
+        <v>-1.7236</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7278</v>
+        <v>0.256</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8453</v>
+        <v>-1.9797</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1925</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7556</v>
+        <v>0.1494</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5702</v>
+        <v>0.0984</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1854</v>
+        <v>0.051</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1444</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6852</v>
+        <v>-1.9968</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.035</v>
+        <v>-0.4138</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6502</v>
+        <v>-1.583</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4905</v>
@@ -1234,13 +1234,13 @@
         <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5685</v>
+        <v>0.1199</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1336</v>
+        <v>0.4876</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4349</v>
+        <v>-0.3677</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3943</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2532</v>
+        <v>-2.4282</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7549</v>
+        <v>-4.1651</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5017</v>
+        <v>1.7369</v>
       </c>
       <c r="G11" t="n">
         <v>-4.3688</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.315</v>
+        <v>0.51</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6642</v>
+        <v>-0.0745</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3492</v>
+        <v>0.5845</v>
       </c>
       <c r="V11" t="n">
         <v>2.8223</v>
@@ -1345,25 +1345,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.4109</v>
+        <v>5.157899999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>4.100499999999999</v>
+        <v>4.847399999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3103</v>
+        <v>0.3102999999999998</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6248000000000005</v>
+        <v>-0.6247999999999996</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9480000000000004</v>
+        <v>0.9479999999999995</v>
       </c>
       <c r="I12" t="n">
         <v>-1.5726</v>
       </c>
       <c r="J12" t="n">
-        <v>7.739100000000001</v>
+        <v>7.7391</v>
       </c>
       <c r="K12" t="n">
         <v>2.704599999999999</v>
@@ -1381,7 +1381,7 @@
         <v>-6.607200000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.000100000000000211</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="Q12" t="n">
         <v>-18.5563</v>
@@ -1390,10 +1390,10 @@
         <v>18.5562</v>
       </c>
       <c r="S12" t="n">
-        <v>3.852599999999999</v>
+        <v>4.5994</v>
       </c>
       <c r="T12" t="n">
-        <v>4.7004</v>
+        <v>5.4472</v>
       </c>
       <c r="U12" t="n">
         <v>-0.8478000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.6093</v>
+        <v>5.7438</v>
       </c>
       <c r="E13" t="n">
         <v>5.7677</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1583</v>
+        <v>-0.0239</v>
       </c>
       <c r="G13" t="n">
         <v>2.8747</v>
@@ -1468,13 +1468,13 @@
         <v>2.7834</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.268</v>
+        <v>-0.1336</v>
       </c>
       <c r="T13" t="n">
         <v>-0.1019</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1661</v>
+        <v>-0.0316</v>
       </c>
       <c r="V13" t="n">
         <v>2.5387</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1762</v>
+        <v>3.5466</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5571</v>
+        <v>1.793</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6191</v>
+        <v>1.7535</v>
       </c>
       <c r="G14" t="n">
         <v>1.6016</v>
@@ -1546,13 +1546,13 @@
         <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1186</v>
+        <v>0.2517</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3462</v>
+        <v>0.5821</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4648</v>
+        <v>-0.3304</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3943</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. BIRSEN</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8401</v>
+        <v>0.5361</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0132</v>
+        <v>1.1858</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.173</v>
+        <v>-0.6498</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4455</v>
+        <v>1.1716</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.456</v>
+        <v>0.1611</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9015</v>
+        <v>1.0106</v>
       </c>
       <c r="J15" t="n">
-        <v>5.1042</v>
+        <v>1.3043</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3564</v>
+        <v>0.605</v>
       </c>
       <c r="L15" t="n">
-        <v>4.7478</v>
+        <v>0.6993</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6587</v>
+        <v>-0.1326</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8123</v>
+        <v>-0.4439</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8464</v>
+        <v>0.3113</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5544</v>
+        <v>-0.3804</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3882</v>
+        <v>-0.0077</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8338</v>
+        <v>-0.3727</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0722</v>
+        <v>-1.1829</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.1107</v>
       </c>
       <c r="X15" t="n">
         <v>-1.0722</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. SILVA</t>
+          <t>M. BIRSEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0466</v>
+        <v>0.2504</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4669</v>
+        <v>1.9516</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4202</v>
+        <v>-1.7012</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2362</v>
+        <v>3.4455</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8714</v>
+        <v>-0.456</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3648</v>
+        <v>3.9015</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6</v>
+        <v>5.1042</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6</v>
+        <v>0.3564</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>4.7478</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6362</v>
+        <v>-1.6587</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2714</v>
+        <v>-0.8123</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3648</v>
+        <v>-0.8464</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.5515</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q16" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0398</v>
+        <v>-0.0354</v>
       </c>
       <c r="T16" t="n">
-        <v>1.274</v>
+        <v>0.3266</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2341</v>
+        <v>-0.362</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7501</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2648</v>
+        <v>-0.2312</v>
       </c>
       <c r="E17" t="n">
         <v>-0.0043</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2606</v>
+        <v>-0.227</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6765</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0523</v>
+        <v>-0.0187</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4247</v>
+        <v>-0.4088</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5961</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0208</v>
+        <v>-0.4992</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1716</v>
+        <v>-0.3743</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1611</v>
+        <v>-0.3409</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0106</v>
+        <v>-0.0334</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3043</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.605</v>
+        <v>0.0168</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6993</v>
+        <v>0.0736</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1326</v>
+        <v>-0.4647</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4439</v>
+        <v>-0.3577</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3113</v>
+        <v>-0.107</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3412</v>
+        <v>-0.0345</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5975</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7437</v>
+        <v>-0.0345</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1829</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.1107</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>C. SILVA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4652</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09039999999999999</v>
+        <v>-0.3588</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5556</v>
+        <v>-0.431</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3743</v>
+        <v>2.2362</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3409</v>
+        <v>1.8714</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0334</v>
+        <v>0.3648</v>
       </c>
       <c r="J19" t="n">
-        <v>0.09039999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0168</v>
+        <v>1.6</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0736</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4647</v>
+        <v>0.6362</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3577</v>
+        <v>0.2714</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.107</v>
+        <v>0.3648</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.2034</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.4483</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.2449</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6109</v>
+        <v>-0.9937</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6121</v>
+        <v>-1.2684</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0013</v>
+        <v>0.2747</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.7283</v>
+        <v>-2.465</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.45</v>
+        <v>-2.736</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2783</v>
+        <v>0.2711</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.6571</v>
+        <v>-0.8066</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.1742</v>
+        <v>-2.4494</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.4829</v>
+        <v>1.6428</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9288</v>
+        <v>-1.6583</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2759</v>
+        <v>-0.2866</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2046</v>
+        <v>-1.3717</v>
       </c>
       <c r="P20" t="n">
-        <v>2.7834</v>
+        <v>0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7834</v>
+        <v>3.2473</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.666</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0272</v>
+        <v>-0.2867</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6387</v>
+        <v>-0.242</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X20" t="n">
         <v>-1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8865</v>
+        <v>-1.167</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.094</v>
+        <v>-3.2583</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2075</v>
+        <v>2.0913</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.465</v>
+        <v>-3.7283</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.736</v>
+        <v>-2.45</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2711</v>
+        <v>-1.2783</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8066</v>
+        <v>-4.6571</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.4494</v>
+        <v>-2.1742</v>
       </c>
       <c r="L21" t="n">
-        <v>1.6428</v>
+        <v>-2.4829</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6583</v>
+        <v>0.9288</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2866</v>
+        <v>-0.2759</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3717</v>
+        <v>1.2046</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9278</v>
+        <v>2.7834</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.2473</v>
+        <v>2.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4216</v>
+        <v>-0.2221</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1123</v>
+        <v>0.3266</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3093</v>
+        <v>-0.5487</v>
       </c>
       <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.0722</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.1444</v>
       </c>
       <c r="X21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7793</v>
+        <v>-2.0437</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4013</v>
+        <v>-0.0475</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.378</v>
+        <v>-1.9962</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4992</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2801</v>
+        <v>-0.5445</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5975</v>
+        <v>-0.2436</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6827</v>
+        <v>-0.3009</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1406</v>
+        <v>-2.1977</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.164</v>
+        <v>-2.9281</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0234</v>
+        <v>0.7305</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1172</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5415</v>
+        <v>-0.5985</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3339</v>
+        <v>-0.098</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2076</v>
+        <v>-0.5006</v>
       </c>
       <c r="V23" t="n">
         <v>0.1418</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5112</v>
+        <v>-4.2969</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5955</v>
+        <v>-2.3032</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9158</v>
+        <v>-1.9938</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8445</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>1.3333</v>
+        <v>0.5476</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6844</v>
+        <v>-0.0233</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6489</v>
+        <v>0.5709</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.411</v>
+        <v>-2.0519</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6202000000000005</v>
+        <v>0.6198999999999995</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.031000000000001</v>
+        <v>-2.6721</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6246000000000014</v>
+        <v>0.6245999999999996</v>
       </c>
       <c r="H25" t="n">
         <v>-0.9479000000000004</v>
@@ -2395,7 +2395,7 @@
         <v>-5.0346</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.0001000000000006551</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="Q25" t="n">
         <v>-18.5562</v>
@@ -2404,13 +2404,13 @@
         <v>18.5561</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.8527</v>
+        <v>-1.4937</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8478000000000004</v>
+        <v>0.8476999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.7004</v>
+        <v>-2.3414</v>
       </c>
       <c r="V25" t="n">
         <v>-1.1829</v>
